--- a/result.xlsx
+++ b/result.xlsx
@@ -4,16 +4,38 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25800" windowHeight="17655" firstSheet="3" activeTab="6"/>
+    <workbookView windowWidth="25800" windowHeight="17205" firstSheet="21" activeTab="28"/>
   </bookViews>
   <sheets>
     <sheet name="0.0001adam" sheetId="1" r:id="rId1"/>
-    <sheet name="0.0001signOcp" sheetId="2" r:id="rId2"/>
-    <sheet name="0.0001signOcpWithNorm" sheetId="3" r:id="rId3"/>
-    <sheet name="0.0001adamAndOcp" sheetId="4" r:id="rId4"/>
-    <sheet name="0.0001adamAndOcpWithNorm" sheetId="5" r:id="rId5"/>
-    <sheet name="0.0001adamAndSignOcp" sheetId="6" r:id="rId6"/>
-    <sheet name="0.0001adamAndSignOcpWithNorm" sheetId="7" r:id="rId7"/>
+    <sheet name="0.0001adamWithNorm" sheetId="25" r:id="rId2"/>
+    <sheet name="0.0001signOcp" sheetId="2" r:id="rId3"/>
+    <sheet name="0.0001signOcpWithNorm" sheetId="3" r:id="rId4"/>
+    <sheet name="0.0001adamAndOcp" sheetId="4" r:id="rId5"/>
+    <sheet name="0.0001adamAndOcpWithNorm" sheetId="5" r:id="rId6"/>
+    <sheet name="0.0001adamAndSignOcp" sheetId="6" r:id="rId7"/>
+    <sheet name="0.0001adamAndSignOcpWithNorm" sheetId="7" r:id="rId8"/>
+    <sheet name="0.0001ocp" sheetId="26" r:id="rId9"/>
+    <sheet name="0.0001ocpWithNorm" sheetId="27" r:id="rId10"/>
+    <sheet name="0.0005adam" sheetId="8" r:id="rId11"/>
+    <sheet name="0.0005adamWithNorm" sheetId="14" r:id="rId12"/>
+    <sheet name="0.0005signOcp" sheetId="15" r:id="rId13"/>
+    <sheet name="0.0005signOcpWithNorm" sheetId="16" r:id="rId14"/>
+    <sheet name="0.0005adamAndOcp" sheetId="17" r:id="rId15"/>
+    <sheet name="0.0005adamAndOcpWithNorm" sheetId="18" r:id="rId16"/>
+    <sheet name="0.0005adamAndSignOcp" sheetId="9" r:id="rId17"/>
+    <sheet name="0.0005adamAndSignOcpWithNorm" sheetId="10" r:id="rId18"/>
+    <sheet name="0.0005ocp" sheetId="21" r:id="rId19"/>
+    <sheet name="0.0005ocpWithNorm" sheetId="22" r:id="rId20"/>
+    <sheet name="0.005adam" sheetId="12" r:id="rId21"/>
+    <sheet name="0.005adamWithNorm" sheetId="24" r:id="rId22"/>
+    <sheet name="0.005ocp" sheetId="13" r:id="rId23"/>
+    <sheet name="0.005ocpWithNorm" sheetId="23" r:id="rId24"/>
+    <sheet name="0.0002adam" sheetId="28" r:id="rId25"/>
+    <sheet name="0.0002adamAndSIgnOcp" sheetId="29" r:id="rId26"/>
+    <sheet name="0.0003adam" sheetId="30" r:id="rId27"/>
+    <sheet name="0.0003adamAndSignOcp" sheetId="31" r:id="rId28"/>
+    <sheet name="0.0004adam" sheetId="32" r:id="rId29"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="4">
   <si>
     <t>train loss</t>
   </si>
@@ -57,7 +79,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -69,6 +91,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -538,16 +567,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -556,123 +582,132 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1204,8 +1239,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
-    <col min="2" max="2" width="18.125" customWidth="1"/>
-    <col min="3" max="3" width="18.875" customWidth="1"/>
+    <col min="2" max="2" width="18.1333333333333" customWidth="1"/>
+    <col min="3" max="3" width="18.8833333333333" customWidth="1"/>
     <col min="4" max="4" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1403,6 +1438,2146 @@
       </c>
       <c r="D14">
         <v>3.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="22.225" customWidth="1"/>
+    <col min="2" max="2" width="22.8916666666667" customWidth="1"/>
+    <col min="3" max="3" width="19.3333333333333" customWidth="1"/>
+    <col min="4" max="4" width="20.225" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="3">
+        <v>2.75</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1.39</v>
+      </c>
+      <c r="C2" s="3">
+        <v>15.63</v>
+      </c>
+      <c r="D2" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="3">
+        <v>2.74</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1.33</v>
+      </c>
+      <c r="C3" s="3">
+        <v>15.46</v>
+      </c>
+      <c r="D3" s="3">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="3">
+        <v>2.65</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1.31</v>
+      </c>
+      <c r="C4" s="3">
+        <v>14.16</v>
+      </c>
+      <c r="D4" s="3">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="3">
+        <v>2.68</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="C5" s="3">
+        <v>14.63</v>
+      </c>
+      <c r="D5" s="3">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="3">
+        <v>2.66</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1.28</v>
+      </c>
+      <c r="C6" s="3">
+        <v>14.25</v>
+      </c>
+      <c r="D6" s="3">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="3">
+        <v>2.62</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1.28</v>
+      </c>
+      <c r="C7" s="3">
+        <v>13.76</v>
+      </c>
+      <c r="D7" s="3">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="3">
+        <v>2.64</v>
+      </c>
+      <c r="B8" s="3">
+        <v>1.27</v>
+      </c>
+      <c r="C8" s="3">
+        <v>14.01</v>
+      </c>
+      <c r="D8" s="3">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="3">
+        <v>2.62</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1.25</v>
+      </c>
+      <c r="C9" s="3">
+        <v>13.78</v>
+      </c>
+      <c r="D9" s="3">
+        <v>3.51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="B10" s="3">
+        <v>1.27</v>
+      </c>
+      <c r="C10" s="3">
+        <v>13.37</v>
+      </c>
+      <c r="D10" s="3">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="B11" s="3">
+        <v>1.25</v>
+      </c>
+      <c r="C11" s="3">
+        <v>13.33</v>
+      </c>
+      <c r="D11" s="3">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="3">
+        <v>2.54</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1.25</v>
+      </c>
+      <c r="C12" s="3">
+        <v>12.65</v>
+      </c>
+      <c r="D12" s="3">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="3">
+        <v>2.58</v>
+      </c>
+      <c r="B13" s="3">
+        <v>1.24</v>
+      </c>
+      <c r="C13" s="3">
+        <v>13.24</v>
+      </c>
+      <c r="D13" s="3">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="B14" s="3">
+        <v>1.24</v>
+      </c>
+      <c r="C14" s="3">
+        <v>13.32</v>
+      </c>
+      <c r="D14" s="3">
+        <v>3.45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="18.25" customWidth="1"/>
+    <col min="2" max="2" width="18.6333333333333" customWidth="1"/>
+    <col min="3" max="3" width="16.75" customWidth="1"/>
+    <col min="4" max="4" width="30.3833333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>2.62</v>
+      </c>
+      <c r="B2">
+        <v>1.26</v>
+      </c>
+      <c r="C2">
+        <v>13.69</v>
+      </c>
+      <c r="D2">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>2.61</v>
+      </c>
+      <c r="B3">
+        <v>1.24</v>
+      </c>
+      <c r="C3">
+        <v>13.61</v>
+      </c>
+      <c r="D3">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>2.51</v>
+      </c>
+      <c r="B4">
+        <v>1.21</v>
+      </c>
+      <c r="C4">
+        <v>12.37</v>
+      </c>
+      <c r="D4">
+        <v>3.35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>2.56</v>
+      </c>
+      <c r="B5">
+        <v>1.19</v>
+      </c>
+      <c r="C5">
+        <v>12.94</v>
+      </c>
+      <c r="D5">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>2.54</v>
+      </c>
+      <c r="B6">
+        <v>1.21</v>
+      </c>
+      <c r="C6">
+        <v>12.68</v>
+      </c>
+      <c r="D6">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>2.5</v>
+      </c>
+      <c r="B7">
+        <v>1.19</v>
+      </c>
+      <c r="C7">
+        <v>12.23</v>
+      </c>
+      <c r="D7">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>2.53</v>
+      </c>
+      <c r="B8">
+        <v>1.17</v>
+      </c>
+      <c r="C8">
+        <v>12.52</v>
+      </c>
+      <c r="D8">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>2.5</v>
+      </c>
+      <c r="B9">
+        <v>1.17</v>
+      </c>
+      <c r="C9">
+        <v>12.14</v>
+      </c>
+      <c r="D9">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>2.49</v>
+      </c>
+      <c r="B10">
+        <v>1.18</v>
+      </c>
+      <c r="C10">
+        <v>12.02</v>
+      </c>
+      <c r="D10">
+        <v>3.26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>2.49</v>
+      </c>
+      <c r="B11">
+        <v>1.19</v>
+      </c>
+      <c r="C11">
+        <v>12.04</v>
+      </c>
+      <c r="D11">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>2.43</v>
+      </c>
+      <c r="B12">
+        <v>1.17</v>
+      </c>
+      <c r="C12">
+        <v>11.33</v>
+      </c>
+      <c r="D12">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>2.48</v>
+      </c>
+      <c r="B13">
+        <v>1.17</v>
+      </c>
+      <c r="C13">
+        <v>11.97</v>
+      </c>
+      <c r="D13">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>2.49</v>
+      </c>
+      <c r="B14">
+        <v>1.16</v>
+      </c>
+      <c r="C14">
+        <v>12.07</v>
+      </c>
+      <c r="D14">
+        <v>3.19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="18.8833333333333" customWidth="1"/>
+    <col min="2" max="2" width="17.3833333333333" customWidth="1"/>
+    <col min="3" max="3" width="15.1333333333333" customWidth="1"/>
+    <col min="4" max="4" width="21.1333333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>2.62</v>
+      </c>
+      <c r="B2">
+        <v>1.25</v>
+      </c>
+      <c r="C2">
+        <v>13.68</v>
+      </c>
+      <c r="D2">
+        <v>3.51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>2.61</v>
+      </c>
+      <c r="B3">
+        <v>1.25</v>
+      </c>
+      <c r="C3">
+        <v>13.62</v>
+      </c>
+      <c r="D3">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>2.51</v>
+      </c>
+      <c r="B4">
+        <v>1.21</v>
+      </c>
+      <c r="C4">
+        <v>12.35</v>
+      </c>
+      <c r="D4">
+        <v>3.35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>2.56</v>
+      </c>
+      <c r="B5">
+        <v>1.2</v>
+      </c>
+      <c r="C5">
+        <v>12.91</v>
+      </c>
+      <c r="D5">
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>2.54</v>
+      </c>
+      <c r="B6">
+        <v>1.2</v>
+      </c>
+      <c r="C6">
+        <v>12.68</v>
+      </c>
+      <c r="D6">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>2.5</v>
+      </c>
+      <c r="B7">
+        <v>1.19</v>
+      </c>
+      <c r="C7">
+        <v>12.21</v>
+      </c>
+      <c r="D7">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>2.53</v>
+      </c>
+      <c r="B8">
+        <v>1.17</v>
+      </c>
+      <c r="C8">
+        <v>12.5</v>
+      </c>
+      <c r="D8">
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>2.5</v>
+      </c>
+      <c r="B9">
+        <v>1.17</v>
+      </c>
+      <c r="C9">
+        <v>12.18</v>
+      </c>
+      <c r="D9">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>2.48</v>
+      </c>
+      <c r="B10">
+        <v>1.18</v>
+      </c>
+      <c r="C10">
+        <v>11.99</v>
+      </c>
+      <c r="D10">
+        <v>3.26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>2.49</v>
+      </c>
+      <c r="B11">
+        <v>1.19</v>
+      </c>
+      <c r="C11">
+        <v>12.05</v>
+      </c>
+      <c r="D11">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>2.43</v>
+      </c>
+      <c r="B12">
+        <v>1.17</v>
+      </c>
+      <c r="C12">
+        <v>11.34</v>
+      </c>
+      <c r="D12">
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>2.49</v>
+      </c>
+      <c r="B13">
+        <v>1.17</v>
+      </c>
+      <c r="C13">
+        <v>12</v>
+      </c>
+      <c r="D13">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>2.49</v>
+      </c>
+      <c r="B14">
+        <v>1.16</v>
+      </c>
+      <c r="C14">
+        <v>12.07</v>
+      </c>
+      <c r="D14">
+        <v>3.19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="19.25" customWidth="1"/>
+    <col min="2" max="2" width="17.3833333333333" customWidth="1"/>
+    <col min="3" max="3" width="19.1333333333333" customWidth="1"/>
+    <col min="4" max="4" width="19.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>3.49</v>
+      </c>
+      <c r="B2">
+        <v>1.98</v>
+      </c>
+      <c r="C2">
+        <v>32.8</v>
+      </c>
+      <c r="D2">
+        <v>7.28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>6.26</v>
+      </c>
+      <c r="B3">
+        <v>5.32</v>
+      </c>
+      <c r="C3">
+        <v>522.42</v>
+      </c>
+      <c r="D3">
+        <v>204.64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>6.3</v>
+      </c>
+      <c r="B4">
+        <v>5.35</v>
+      </c>
+      <c r="C4">
+        <v>545.36</v>
+      </c>
+      <c r="D4">
+        <v>210.53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>6.33</v>
+      </c>
+      <c r="B5">
+        <v>5.44</v>
+      </c>
+      <c r="C5">
+        <v>561.38</v>
+      </c>
+      <c r="D5">
+        <v>230.77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>6.33</v>
+      </c>
+      <c r="B6">
+        <v>5.35</v>
+      </c>
+      <c r="C6">
+        <v>559.41</v>
+      </c>
+      <c r="D6">
+        <v>209.83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>6.78</v>
+      </c>
+      <c r="B7">
+        <v>5.87</v>
+      </c>
+      <c r="C7">
+        <v>878.65</v>
+      </c>
+      <c r="D7">
+        <v>354.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>6.59</v>
+      </c>
+      <c r="B8">
+        <v>5.61</v>
+      </c>
+      <c r="C8">
+        <v>725.83</v>
+      </c>
+      <c r="D8">
+        <v>273.85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>6.54</v>
+      </c>
+      <c r="B9">
+        <v>5.56</v>
+      </c>
+      <c r="C9">
+        <v>691.35</v>
+      </c>
+      <c r="D9">
+        <v>260.17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>6.54</v>
+      </c>
+      <c r="B10">
+        <v>5.53</v>
+      </c>
+      <c r="C10">
+        <v>691.79</v>
+      </c>
+      <c r="D10">
+        <v>253.09</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>6.46</v>
+      </c>
+      <c r="B11">
+        <v>5.53</v>
+      </c>
+      <c r="C11">
+        <v>637.39</v>
+      </c>
+      <c r="D11">
+        <v>252.59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>6.36</v>
+      </c>
+      <c r="B12">
+        <v>5.45</v>
+      </c>
+      <c r="C12">
+        <v>578.42</v>
+      </c>
+      <c r="D12">
+        <v>232.21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>6.36</v>
+      </c>
+      <c r="B13">
+        <v>5.38</v>
+      </c>
+      <c r="C13">
+        <v>577.31</v>
+      </c>
+      <c r="D13">
+        <v>217.31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>6.37</v>
+      </c>
+      <c r="B14">
+        <v>5.35</v>
+      </c>
+      <c r="C14">
+        <v>585.32</v>
+      </c>
+      <c r="D14">
+        <v>209.94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="20.75" customWidth="1"/>
+    <col min="2" max="2" width="18.8833333333333" customWidth="1"/>
+    <col min="3" max="3" width="16.5" customWidth="1"/>
+    <col min="4" max="4" width="18.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>3.4</v>
+      </c>
+      <c r="B2">
+        <v>1.88</v>
+      </c>
+      <c r="C2">
+        <v>30.09</v>
+      </c>
+      <c r="D2">
+        <v>6.58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>6.16</v>
+      </c>
+      <c r="B3">
+        <v>5.1</v>
+      </c>
+      <c r="C3">
+        <v>471.45</v>
+      </c>
+      <c r="D3">
+        <v>164.41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>6.23</v>
+      </c>
+      <c r="B4">
+        <v>5.23</v>
+      </c>
+      <c r="C4">
+        <v>508.17</v>
+      </c>
+      <c r="D4">
+        <v>186.92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>6.34</v>
+      </c>
+      <c r="B5">
+        <v>5.38</v>
+      </c>
+      <c r="C5">
+        <v>566.28</v>
+      </c>
+      <c r="D5">
+        <v>217.05</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>6.32</v>
+      </c>
+      <c r="B6">
+        <v>5.34</v>
+      </c>
+      <c r="C6">
+        <v>554.73</v>
+      </c>
+      <c r="D6">
+        <v>208.76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>6.28</v>
+      </c>
+      <c r="B7">
+        <v>5.34</v>
+      </c>
+      <c r="C7">
+        <v>534.27</v>
+      </c>
+      <c r="D7">
+        <v>208.81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>6.34</v>
+      </c>
+      <c r="B8">
+        <v>5.35</v>
+      </c>
+      <c r="C8">
+        <v>567.17</v>
+      </c>
+      <c r="D8">
+        <v>210.78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>6.28</v>
+      </c>
+      <c r="B9">
+        <v>5.29</v>
+      </c>
+      <c r="C9">
+        <v>533.34</v>
+      </c>
+      <c r="D9">
+        <v>197.74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>6.26</v>
+      </c>
+      <c r="B10">
+        <v>5.26</v>
+      </c>
+      <c r="C10">
+        <v>523.37</v>
+      </c>
+      <c r="D10">
+        <v>193.19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>6.29</v>
+      </c>
+      <c r="B11">
+        <v>5.39</v>
+      </c>
+      <c r="C11">
+        <v>540.75</v>
+      </c>
+      <c r="D11">
+        <v>219.95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>6.26</v>
+      </c>
+      <c r="B12">
+        <v>5.33</v>
+      </c>
+      <c r="C12">
+        <v>522.04</v>
+      </c>
+      <c r="D12">
+        <v>205.54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>6.31</v>
+      </c>
+      <c r="B13">
+        <v>5.36</v>
+      </c>
+      <c r="C13">
+        <v>551.11</v>
+      </c>
+      <c r="D13">
+        <v>212.41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>6.33</v>
+      </c>
+      <c r="B14">
+        <v>5.36</v>
+      </c>
+      <c r="C14">
+        <v>562.28</v>
+      </c>
+      <c r="D14">
+        <v>212.02</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="21.75" customWidth="1"/>
+    <col min="2" max="2" width="19.3833333333333" customWidth="1"/>
+    <col min="3" max="3" width="15.5" customWidth="1"/>
+    <col min="4" max="4" width="17.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>2.66</v>
+      </c>
+      <c r="B2">
+        <v>1.27</v>
+      </c>
+      <c r="C2">
+        <v>14.24</v>
+      </c>
+      <c r="D2">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>2.64</v>
+      </c>
+      <c r="B3">
+        <v>1.27</v>
+      </c>
+      <c r="C3">
+        <v>14.01</v>
+      </c>
+      <c r="D3">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>2.54</v>
+      </c>
+      <c r="B4">
+        <v>1.22</v>
+      </c>
+      <c r="C4">
+        <v>12.69</v>
+      </c>
+      <c r="D4">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>2.58</v>
+      </c>
+      <c r="B5">
+        <v>1.2</v>
+      </c>
+      <c r="C5">
+        <v>13.17</v>
+      </c>
+      <c r="D5">
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>2.55</v>
+      </c>
+      <c r="B6">
+        <v>1.22</v>
+      </c>
+      <c r="C6">
+        <v>12.86</v>
+      </c>
+      <c r="D6">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>2.52</v>
+      </c>
+      <c r="B7">
+        <v>1.19</v>
+      </c>
+      <c r="C7">
+        <v>12.4</v>
+      </c>
+      <c r="D7">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>2.54</v>
+      </c>
+      <c r="B8">
+        <v>1.18</v>
+      </c>
+      <c r="C8">
+        <v>12.64</v>
+      </c>
+      <c r="D8">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>2.51</v>
+      </c>
+      <c r="B9">
+        <v>1.19</v>
+      </c>
+      <c r="C9">
+        <v>12.32</v>
+      </c>
+      <c r="D9">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>2.5</v>
+      </c>
+      <c r="B10">
+        <v>1.18</v>
+      </c>
+      <c r="C10">
+        <v>12.13</v>
+      </c>
+      <c r="D10">
+        <v>3.26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>2.49</v>
+      </c>
+      <c r="B11">
+        <v>1.18</v>
+      </c>
+      <c r="C11">
+        <v>12.11</v>
+      </c>
+      <c r="D11">
+        <v>3.26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>2.43</v>
+      </c>
+      <c r="B12">
+        <v>1.17</v>
+      </c>
+      <c r="C12">
+        <v>11.4</v>
+      </c>
+      <c r="D12">
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>2.49</v>
+      </c>
+      <c r="B13">
+        <v>1.16</v>
+      </c>
+      <c r="C13">
+        <v>12.03</v>
+      </c>
+      <c r="D13">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>2.49</v>
+      </c>
+      <c r="B14">
+        <v>1.17</v>
+      </c>
+      <c r="C14">
+        <v>12.08</v>
+      </c>
+      <c r="D14">
+        <v>3.21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="23.75" customWidth="1"/>
+    <col min="2" max="2" width="21.1333333333333" customWidth="1"/>
+    <col min="3" max="3" width="19.6333333333333" customWidth="1"/>
+    <col min="4" max="4" width="25.3833333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>2.75</v>
+      </c>
+      <c r="B2">
+        <v>1.37</v>
+      </c>
+      <c r="C2">
+        <v>15.62</v>
+      </c>
+      <c r="D2">
+        <v>3.93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>2.79</v>
+      </c>
+      <c r="B3">
+        <v>1.41</v>
+      </c>
+      <c r="C3">
+        <v>16.24</v>
+      </c>
+      <c r="D3">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>2.72</v>
+      </c>
+      <c r="B4">
+        <v>1.36</v>
+      </c>
+      <c r="C4">
+        <v>15.24</v>
+      </c>
+      <c r="D4">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>2.78</v>
+      </c>
+      <c r="B5">
+        <v>1.34</v>
+      </c>
+      <c r="C5">
+        <v>16.17</v>
+      </c>
+      <c r="D5">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>2.78</v>
+      </c>
+      <c r="B6">
+        <v>1.38</v>
+      </c>
+      <c r="C6">
+        <v>16.15</v>
+      </c>
+      <c r="D6">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>2.76</v>
+      </c>
+      <c r="B7">
+        <v>1.39</v>
+      </c>
+      <c r="C7">
+        <v>15.87</v>
+      </c>
+      <c r="D7">
+        <v>4.03</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>2.82</v>
+      </c>
+      <c r="B8">
+        <v>1.36</v>
+      </c>
+      <c r="C8">
+        <v>16.75</v>
+      </c>
+      <c r="D8">
+        <v>3.91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>2.81</v>
+      </c>
+      <c r="B9">
+        <v>1.43</v>
+      </c>
+      <c r="C9">
+        <v>16.61</v>
+      </c>
+      <c r="D9">
+        <v>4.18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>2.8</v>
+      </c>
+      <c r="B10">
+        <v>1.42</v>
+      </c>
+      <c r="C10">
+        <v>16.52</v>
+      </c>
+      <c r="D10">
+        <v>4.16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>3.02</v>
+      </c>
+      <c r="B11">
+        <v>2.04</v>
+      </c>
+      <c r="C11">
+        <v>20.4</v>
+      </c>
+      <c r="D11">
+        <v>7.66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>3.16</v>
+      </c>
+      <c r="B12">
+        <v>1.48</v>
+      </c>
+      <c r="C12">
+        <v>23.69</v>
+      </c>
+      <c r="D12">
+        <v>4.39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>2.87</v>
+      </c>
+      <c r="B13">
+        <v>1.43</v>
+      </c>
+      <c r="C13">
+        <v>17.66</v>
+      </c>
+      <c r="D13">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>2.91</v>
+      </c>
+      <c r="B14">
+        <v>1.49</v>
+      </c>
+      <c r="C14">
+        <v>18.31</v>
+      </c>
+      <c r="D14">
+        <v>4.43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="22.5" customWidth="1"/>
+    <col min="2" max="2" width="19.8833333333333" customWidth="1"/>
+    <col min="3" max="3" width="18.5" customWidth="1"/>
+    <col min="4" max="4" width="23.3833333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>2.63</v>
+      </c>
+      <c r="B2">
+        <v>1.26</v>
+      </c>
+      <c r="C2">
+        <v>13.82</v>
+      </c>
+      <c r="D2">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>2.61</v>
+      </c>
+      <c r="B3">
+        <v>1.24</v>
+      </c>
+      <c r="C3">
+        <v>13.67</v>
+      </c>
+      <c r="D3">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>2.52</v>
+      </c>
+      <c r="B4">
+        <v>1.21</v>
+      </c>
+      <c r="C4">
+        <v>12.47</v>
+      </c>
+      <c r="D4">
+        <v>3.36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>2.56</v>
+      </c>
+      <c r="B5">
+        <v>1.2</v>
+      </c>
+      <c r="C5">
+        <v>12.98</v>
+      </c>
+      <c r="D5">
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>2.55</v>
+      </c>
+      <c r="B6">
+        <v>1.22</v>
+      </c>
+      <c r="C6">
+        <v>12.75</v>
+      </c>
+      <c r="D6">
+        <v>3.37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>2.51</v>
+      </c>
+      <c r="B7">
+        <v>1.19</v>
+      </c>
+      <c r="C7">
+        <v>12.28</v>
+      </c>
+      <c r="D7">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>2.54</v>
+      </c>
+      <c r="B8">
+        <v>1.18</v>
+      </c>
+      <c r="C8">
+        <v>12.63</v>
+      </c>
+      <c r="D8">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>2.5</v>
+      </c>
+      <c r="B9">
+        <v>1.19</v>
+      </c>
+      <c r="C9">
+        <v>12.2</v>
+      </c>
+      <c r="D9">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>2.49</v>
+      </c>
+      <c r="B10">
+        <v>1.18</v>
+      </c>
+      <c r="C10">
+        <v>12.12</v>
+      </c>
+      <c r="D10">
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>2.49</v>
+      </c>
+      <c r="B11">
+        <v>1.19</v>
+      </c>
+      <c r="C11">
+        <v>12.1</v>
+      </c>
+      <c r="D11">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>2.44</v>
+      </c>
+      <c r="B12">
+        <v>1.18</v>
+      </c>
+      <c r="C12">
+        <v>11.42</v>
+      </c>
+      <c r="D12">
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>2.49</v>
+      </c>
+      <c r="B13">
+        <v>1.16</v>
+      </c>
+      <c r="C13">
+        <v>12.04</v>
+      </c>
+      <c r="D13">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>2.5</v>
+      </c>
+      <c r="B14">
+        <v>1.17</v>
+      </c>
+      <c r="C14">
+        <v>12.15</v>
+      </c>
+      <c r="D14">
+        <v>3.21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="20.25" customWidth="1"/>
+    <col min="2" max="2" width="18.5" customWidth="1"/>
+    <col min="3" max="3" width="18.3833333333333" customWidth="1"/>
+    <col min="4" max="4" width="18.8833333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>2.61</v>
+      </c>
+      <c r="B2">
+        <v>1.26</v>
+      </c>
+      <c r="C2">
+        <v>13.66</v>
+      </c>
+      <c r="D2">
+        <v>3.51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>2.61</v>
+      </c>
+      <c r="B3">
+        <v>1.24</v>
+      </c>
+      <c r="C3">
+        <v>13.58</v>
+      </c>
+      <c r="D3">
+        <v>3.44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>2.52</v>
+      </c>
+      <c r="B4">
+        <v>1.21</v>
+      </c>
+      <c r="C4">
+        <v>12.43</v>
+      </c>
+      <c r="D4">
+        <v>3.36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>2.56</v>
+      </c>
+      <c r="B5">
+        <v>1.2</v>
+      </c>
+      <c r="C5">
+        <v>12.96</v>
+      </c>
+      <c r="D5">
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>2.55</v>
+      </c>
+      <c r="B6">
+        <v>1.2</v>
+      </c>
+      <c r="C6">
+        <v>12.75</v>
+      </c>
+      <c r="D6">
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>2.51</v>
+      </c>
+      <c r="B7">
+        <v>1.18</v>
+      </c>
+      <c r="C7">
+        <v>12.28</v>
+      </c>
+      <c r="D7">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>2.53</v>
+      </c>
+      <c r="B8">
+        <v>1.18</v>
+      </c>
+      <c r="C8">
+        <v>12.59</v>
+      </c>
+      <c r="D8">
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>2.5</v>
+      </c>
+      <c r="B9">
+        <v>1.18</v>
+      </c>
+      <c r="C9">
+        <v>12.23</v>
+      </c>
+      <c r="D9">
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>2.49</v>
+      </c>
+      <c r="B10">
+        <v>1.18</v>
+      </c>
+      <c r="C10">
+        <v>12.06</v>
+      </c>
+      <c r="D10">
+        <v>3.26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>2.49</v>
+      </c>
+      <c r="B11">
+        <v>1.21</v>
+      </c>
+      <c r="C11">
+        <v>12.11</v>
+      </c>
+      <c r="D11">
+        <v>3.35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>2.44</v>
+      </c>
+      <c r="B12">
+        <v>1.18</v>
+      </c>
+      <c r="C12">
+        <v>11.46</v>
+      </c>
+      <c r="D12">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>2.49</v>
+      </c>
+      <c r="B13">
+        <v>1.18</v>
+      </c>
+      <c r="C13">
+        <v>12.1</v>
+      </c>
+      <c r="D13">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>2.5</v>
+      </c>
+      <c r="B14">
+        <v>1.17</v>
+      </c>
+      <c r="C14">
+        <v>12.2</v>
+      </c>
+      <c r="D14">
+        <v>3.21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="22.3833333333333" customWidth="1"/>
+    <col min="2" max="2" width="29" customWidth="1"/>
+    <col min="3" max="3" width="24.8833333333333" customWidth="1"/>
+    <col min="4" max="4" width="19.8833333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>2.76</v>
+      </c>
+      <c r="B2">
+        <v>1.39</v>
+      </c>
+      <c r="C2">
+        <v>15.83</v>
+      </c>
+      <c r="D2">
+        <v>4.01</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>2.74</v>
+      </c>
+      <c r="B3">
+        <v>1.34</v>
+      </c>
+      <c r="C3">
+        <v>15.51</v>
+      </c>
+      <c r="D3">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>2.65</v>
+      </c>
+      <c r="B4">
+        <v>1.31</v>
+      </c>
+      <c r="C4">
+        <v>14.15</v>
+      </c>
+      <c r="D4">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>2.68</v>
+      </c>
+      <c r="B5">
+        <v>1.3</v>
+      </c>
+      <c r="C5">
+        <v>14.63</v>
+      </c>
+      <c r="D5">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>2.66</v>
+      </c>
+      <c r="B6">
+        <v>1.28</v>
+      </c>
+      <c r="C6">
+        <v>14.25</v>
+      </c>
+      <c r="D6">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>2.62</v>
+      </c>
+      <c r="B7">
+        <v>1.29</v>
+      </c>
+      <c r="C7">
+        <v>13.76</v>
+      </c>
+      <c r="D7">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>2.64</v>
+      </c>
+      <c r="B8">
+        <v>1.27</v>
+      </c>
+      <c r="C8">
+        <v>13.95</v>
+      </c>
+      <c r="D8">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>2.62</v>
+      </c>
+      <c r="B9">
+        <v>1.26</v>
+      </c>
+      <c r="C9">
+        <v>13.74</v>
+      </c>
+      <c r="D9">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>2.59</v>
+      </c>
+      <c r="B10">
+        <v>1.26</v>
+      </c>
+      <c r="C10">
+        <v>13.33</v>
+      </c>
+      <c r="D10">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>2.59</v>
+      </c>
+      <c r="B11">
+        <v>1.25</v>
+      </c>
+      <c r="C11">
+        <v>13.27</v>
+      </c>
+      <c r="D11">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>2.53</v>
+      </c>
+      <c r="B12">
+        <v>1.24</v>
+      </c>
+      <c r="C12">
+        <v>12.57</v>
+      </c>
+      <c r="D12">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>2.58</v>
+      </c>
+      <c r="B13">
+        <v>1.23</v>
+      </c>
+      <c r="C13">
+        <v>13.18</v>
+      </c>
+      <c r="D13">
+        <v>3.44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>2.58</v>
+      </c>
+      <c r="B14">
+        <v>1.23</v>
+      </c>
+      <c r="C14">
+        <v>13.2</v>
+      </c>
+      <c r="D14">
+        <v>3.42</v>
       </c>
     </row>
   </sheetData>
@@ -1415,12 +3590,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="17.5" customWidth="1"/>
-    <col min="2" max="2" width="16.375" customWidth="1"/>
-    <col min="3" max="3" width="17.625" customWidth="1"/>
-    <col min="4" max="4" width="21.25" customWidth="1"/>
+    <col min="1" max="1" width="24.225" customWidth="1"/>
+    <col min="2" max="2" width="25.1083333333333" customWidth="1"/>
+    <col min="3" max="3" width="25.225" customWidth="1"/>
+    <col min="4" max="4" width="26.775" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1439,16 +3614,1514 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2">
+        <v>2.7</v>
+      </c>
+      <c r="B2">
+        <v>1.34</v>
+      </c>
+      <c r="C2">
+        <v>14.81</v>
+      </c>
+      <c r="D2">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>2.68</v>
+      </c>
+      <c r="B3">
+        <v>1.29</v>
+      </c>
+      <c r="C3">
+        <v>14.63</v>
+      </c>
+      <c r="D3">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>2.59</v>
+      </c>
+      <c r="B4">
+        <v>1.26</v>
+      </c>
+      <c r="C4">
+        <v>13.34</v>
+      </c>
+      <c r="D4">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>2.63</v>
+      </c>
+      <c r="B5">
+        <v>1.25</v>
+      </c>
+      <c r="C5">
+        <v>13.84</v>
+      </c>
+      <c r="D5">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>2.6</v>
+      </c>
+      <c r="B6">
+        <v>1.23</v>
+      </c>
+      <c r="C6">
+        <v>13.42</v>
+      </c>
+      <c r="D6">
+        <v>3.41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>2.56</v>
+      </c>
+      <c r="B7">
+        <v>1.24</v>
+      </c>
+      <c r="C7">
+        <v>12.92</v>
+      </c>
+      <c r="D7">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>2.57</v>
+      </c>
+      <c r="B8">
+        <v>1.21</v>
+      </c>
+      <c r="C8">
+        <v>13.12</v>
+      </c>
+      <c r="D8">
+        <v>3.36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>2.55</v>
+      </c>
+      <c r="B9">
+        <v>1.21</v>
+      </c>
+      <c r="C9">
+        <v>12.81</v>
+      </c>
+      <c r="D9">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>2.52</v>
+      </c>
+      <c r="B10">
+        <v>1.21</v>
+      </c>
+      <c r="C10">
+        <v>12.49</v>
+      </c>
+      <c r="D10">
+        <v>3.35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>2.52</v>
+      </c>
+      <c r="B11">
+        <v>1.2</v>
+      </c>
+      <c r="C11">
+        <v>12.49</v>
+      </c>
+      <c r="D11">
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>2.47</v>
+      </c>
+      <c r="B12">
+        <v>1.19</v>
+      </c>
+      <c r="C12">
+        <v>11.78</v>
+      </c>
+      <c r="D12">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>2.51</v>
+      </c>
+      <c r="B13">
+        <v>1.18</v>
+      </c>
+      <c r="C13">
+        <v>12.34</v>
+      </c>
+      <c r="D13">
+        <v>3.26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>2.52</v>
+      </c>
+      <c r="B14">
+        <v>1.18</v>
+      </c>
+      <c r="C14">
+        <v>12.41</v>
+      </c>
+      <c r="D14">
+        <v>3.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="17.8833333333333" customWidth="1"/>
+    <col min="2" max="2" width="21.5" customWidth="1"/>
+    <col min="3" max="3" width="23" customWidth="1"/>
+    <col min="4" max="4" width="21.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>2.67</v>
+      </c>
+      <c r="B2">
+        <v>1.3</v>
+      </c>
+      <c r="C2">
+        <v>14.49</v>
+      </c>
+      <c r="D2">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="3" s="2" customFormat="1" spans="1:4">
+      <c r="A3" s="2">
+        <v>2.63</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1.24</v>
+      </c>
+      <c r="C3" s="2">
+        <v>13.83</v>
+      </c>
+      <c r="D3" s="2">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" spans="1:4">
+      <c r="A4" s="2">
+        <v>2.63</v>
+      </c>
+      <c r="B4" s="2">
+        <v>1.24</v>
+      </c>
+      <c r="C4" s="2">
+        <v>13.83</v>
+      </c>
+      <c r="D4" s="2">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>2.6</v>
+      </c>
+      <c r="B5">
+        <v>1.22</v>
+      </c>
+      <c r="C5">
+        <v>13.51</v>
+      </c>
+      <c r="D5">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>2.58</v>
+      </c>
+      <c r="B6">
+        <v>1.22</v>
+      </c>
+      <c r="C6">
+        <v>13.22</v>
+      </c>
+      <c r="D6">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>2.54</v>
+      </c>
+      <c r="B7">
+        <v>1.21</v>
+      </c>
+      <c r="C7">
+        <v>12.69</v>
+      </c>
+      <c r="D7">
+        <v>3.35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>2.56</v>
+      </c>
+      <c r="B8">
+        <v>1.2</v>
+      </c>
+      <c r="C8">
+        <v>12.93</v>
+      </c>
+      <c r="D8">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>2.54</v>
+      </c>
+      <c r="B9">
+        <v>1.19</v>
+      </c>
+      <c r="C9">
+        <v>12.64</v>
+      </c>
+      <c r="D9">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>2.51</v>
+      </c>
+      <c r="B10">
+        <v>1.2</v>
+      </c>
+      <c r="C10">
+        <v>12.35</v>
+      </c>
+      <c r="D10">
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>2.51</v>
+      </c>
+      <c r="B11">
+        <v>1.2</v>
+      </c>
+      <c r="C11">
+        <v>12.35</v>
+      </c>
+      <c r="D11">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>2.46</v>
+      </c>
+      <c r="B12">
+        <v>1.18</v>
+      </c>
+      <c r="C12">
+        <v>11.68</v>
+      </c>
+      <c r="D12">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>2.51</v>
+      </c>
+      <c r="B13">
+        <v>1.18</v>
+      </c>
+      <c r="C13">
+        <v>12.25</v>
+      </c>
+      <c r="D13">
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>2.51</v>
+      </c>
+      <c r="B14">
+        <v>1.17</v>
+      </c>
+      <c r="C14">
+        <v>12.35</v>
+      </c>
+      <c r="D14">
+        <v>3.22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="25.1333333333333" customWidth="1"/>
+    <col min="2" max="2" width="17.6333333333333" customWidth="1"/>
+    <col min="3" max="3" width="16.5" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>6.27</v>
+      </c>
+      <c r="B2">
+        <v>5.33</v>
+      </c>
+      <c r="C2">
+        <v>530.45</v>
+      </c>
+      <c r="D2">
+        <v>207.05</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>6.3</v>
+      </c>
+      <c r="B3">
+        <v>5.35</v>
+      </c>
+      <c r="C3">
+        <v>542.64</v>
+      </c>
+      <c r="D3">
+        <v>210.94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>6.22</v>
+      </c>
+      <c r="B4">
+        <v>5.27</v>
+      </c>
+      <c r="C4">
+        <v>501.51</v>
+      </c>
+      <c r="D4">
+        <v>194.07</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>6.26</v>
+      </c>
+      <c r="B5">
+        <v>5.24</v>
+      </c>
+      <c r="C5">
+        <v>525.61</v>
+      </c>
+      <c r="D5">
+        <v>189.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>6.07</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>431.13</v>
+      </c>
+      <c r="D6">
+        <v>148.38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>6.2</v>
+      </c>
+      <c r="B7">
+        <v>5.21</v>
+      </c>
+      <c r="C7">
+        <v>492.1</v>
+      </c>
+      <c r="D7">
+        <v>183.88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>6.1</v>
+      </c>
+      <c r="B8">
+        <v>5.08</v>
+      </c>
+      <c r="C8">
+        <v>443.65</v>
+      </c>
+      <c r="D8">
+        <v>160.53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>6.21</v>
+      </c>
+      <c r="B9">
+        <v>5.27</v>
+      </c>
+      <c r="C9">
+        <v>498.39</v>
+      </c>
+      <c r="D9">
+        <v>193.47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>6.34</v>
+      </c>
+      <c r="B10">
+        <v>5.33</v>
+      </c>
+      <c r="C10">
+        <v>566.88</v>
+      </c>
+      <c r="D10">
+        <v>206.94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>6.24</v>
+      </c>
+      <c r="B11">
+        <v>5.3</v>
+      </c>
+      <c r="C11">
+        <v>512.65</v>
+      </c>
+      <c r="D11">
+        <v>200.13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>6.09</v>
+      </c>
+      <c r="B12">
+        <v>5.12</v>
+      </c>
+      <c r="C12">
+        <v>441.41</v>
+      </c>
+      <c r="D12">
+        <v>167.91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>6.34</v>
+      </c>
+      <c r="B13">
+        <v>5.39</v>
+      </c>
+      <c r="C13">
+        <v>567.19</v>
+      </c>
+      <c r="D13">
+        <v>219.32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>6.32</v>
+      </c>
+      <c r="B14">
+        <v>5.32</v>
+      </c>
+      <c r="C14">
+        <v>554.79</v>
+      </c>
+      <c r="D14">
+        <v>204.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="24.6333333333333" customWidth="1"/>
+    <col min="3" max="3" width="16.1333333333333" customWidth="1"/>
+    <col min="4" max="4" width="37.3833333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>3.04</v>
+      </c>
+      <c r="B2">
+        <v>1.63</v>
+      </c>
+      <c r="C2">
+        <v>20.81</v>
+      </c>
+      <c r="D2">
+        <v>5.11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>4.93</v>
+      </c>
+      <c r="B3">
+        <v>4.49</v>
+      </c>
+      <c r="C3">
+        <v>137.85</v>
+      </c>
+      <c r="D3">
+        <v>88.76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>6.35</v>
+      </c>
+      <c r="B4">
+        <v>5.37</v>
+      </c>
+      <c r="C4">
+        <v>572.7</v>
+      </c>
+      <c r="D4">
+        <v>213.85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>6.36</v>
+      </c>
+      <c r="B5">
+        <v>5.4</v>
+      </c>
+      <c r="C5">
+        <v>577.45</v>
+      </c>
+      <c r="D5">
+        <v>222.26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>6.15</v>
+      </c>
+      <c r="B6">
+        <v>5.1</v>
+      </c>
+      <c r="C6">
+        <v>469.71</v>
+      </c>
+      <c r="D6">
+        <v>164.76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>6.07</v>
+      </c>
+      <c r="B7">
+        <v>5.04</v>
+      </c>
+      <c r="C7">
+        <v>431.77</v>
+      </c>
+      <c r="D7">
+        <v>155.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>6.07</v>
+      </c>
+      <c r="B8">
+        <v>5.12</v>
+      </c>
+      <c r="C8">
+        <v>431.76</v>
+      </c>
+      <c r="D8">
+        <v>167.26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>6.01</v>
+      </c>
+      <c r="B9">
+        <v>4.97</v>
+      </c>
+      <c r="C9">
+        <v>408.05</v>
+      </c>
+      <c r="D9">
+        <v>143.98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>6.3</v>
+      </c>
+      <c r="B10">
+        <v>5.31</v>
+      </c>
+      <c r="C10">
+        <v>543.39</v>
+      </c>
+      <c r="D10">
+        <v>201.54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>6.27</v>
+      </c>
+      <c r="B11">
+        <v>5.34</v>
+      </c>
+      <c r="C11">
+        <v>525.9</v>
+      </c>
+      <c r="D11">
+        <v>208.94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>6.16</v>
+      </c>
+      <c r="B12">
+        <v>5.24</v>
+      </c>
+      <c r="C12">
+        <v>475.73</v>
+      </c>
+      <c r="D12">
+        <v>188.62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>6.33</v>
+      </c>
+      <c r="B13">
+        <v>5.36</v>
+      </c>
+      <c r="C13">
+        <v>561.58</v>
+      </c>
+      <c r="D13">
+        <v>212.22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>6.25</v>
+      </c>
+      <c r="B14">
+        <v>5.24</v>
+      </c>
+      <c r="C14">
+        <v>520.17</v>
+      </c>
+      <c r="D14">
+        <v>187.96</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="32.1333333333333" customWidth="1"/>
+    <col min="2" max="2" width="21.3833333333333" customWidth="1"/>
+    <col min="3" max="3" width="17.75" customWidth="1"/>
+    <col min="4" max="4" width="25.8833333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>2.66</v>
+      </c>
+      <c r="B2">
+        <v>1.29</v>
+      </c>
+      <c r="C2">
+        <v>14.3</v>
+      </c>
+      <c r="D2">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>2.65</v>
+      </c>
+      <c r="B3">
+        <v>1.28</v>
+      </c>
+      <c r="C3">
+        <v>14.17</v>
+      </c>
+      <c r="D3">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>2.55</v>
+      </c>
+      <c r="B4">
+        <v>1.24</v>
+      </c>
+      <c r="C4">
+        <v>12.86</v>
+      </c>
+      <c r="D4">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>2.59</v>
+      </c>
+      <c r="B5">
+        <v>1.22</v>
+      </c>
+      <c r="C5">
+        <v>13.39</v>
+      </c>
+      <c r="D5">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>2.57</v>
+      </c>
+      <c r="B6">
+        <v>1.24</v>
+      </c>
+      <c r="C6">
+        <v>13.13</v>
+      </c>
+      <c r="D6">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>2.54</v>
+      </c>
+      <c r="B7">
+        <v>1.2</v>
+      </c>
+      <c r="C7">
+        <v>12.65</v>
+      </c>
+      <c r="D7">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>2.56</v>
+      </c>
+      <c r="B8">
+        <v>1.2</v>
+      </c>
+      <c r="C8">
+        <v>12.91</v>
+      </c>
+      <c r="D8">
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>2.54</v>
+      </c>
+      <c r="B9">
+        <v>1.19</v>
+      </c>
+      <c r="C9">
+        <v>12.65</v>
+      </c>
+      <c r="D9">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>2.52</v>
+      </c>
+      <c r="B10">
+        <v>1.21</v>
+      </c>
+      <c r="C10">
+        <v>12.4</v>
+      </c>
+      <c r="D10">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>2.52</v>
+      </c>
+      <c r="B11">
+        <v>1.21</v>
+      </c>
+      <c r="C11">
+        <v>12.42</v>
+      </c>
+      <c r="D11">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>2.46</v>
+      </c>
+      <c r="B12">
+        <v>1.2</v>
+      </c>
+      <c r="C12">
+        <v>11.72</v>
+      </c>
+      <c r="D12">
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>2.52</v>
+      </c>
+      <c r="B13">
+        <v>1.18</v>
+      </c>
+      <c r="C13">
+        <v>12.38</v>
+      </c>
+      <c r="D13">
+        <v>3.26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>2.52</v>
+      </c>
+      <c r="B14">
+        <v>1.18</v>
+      </c>
+      <c r="C14">
+        <v>12.42</v>
+      </c>
+      <c r="D14">
+        <v>3.26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="18.8833333333333" customWidth="1"/>
+    <col min="2" max="2" width="18.5" customWidth="1"/>
+    <col min="3" max="3" width="20.5" customWidth="1"/>
+    <col min="4" max="4" width="23.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>2.73</v>
+      </c>
+      <c r="B2">
+        <v>1.39</v>
+      </c>
+      <c r="C2">
+        <v>15.37</v>
+      </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>2.74</v>
+      </c>
+      <c r="B3">
+        <v>1.35</v>
+      </c>
+      <c r="C3">
+        <v>15.42</v>
+      </c>
+      <c r="D3">
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>2.67</v>
+      </c>
+      <c r="B4">
+        <v>1.31</v>
+      </c>
+      <c r="C4">
+        <v>14.42</v>
+      </c>
+      <c r="D4">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>2.71</v>
+      </c>
+      <c r="B5">
+        <v>1.34</v>
+      </c>
+      <c r="C5">
+        <v>15.06</v>
+      </c>
+      <c r="D5">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>2.7</v>
+      </c>
+      <c r="B6">
+        <v>1.33</v>
+      </c>
+      <c r="C6">
+        <v>14.86</v>
+      </c>
+      <c r="D6">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>2.68</v>
+      </c>
+      <c r="B7">
+        <v>1.28</v>
+      </c>
+      <c r="C7">
+        <v>14.53</v>
+      </c>
+      <c r="D7">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>2.71</v>
+      </c>
+      <c r="B8">
+        <v>1.28</v>
+      </c>
+      <c r="C8">
+        <v>14.98</v>
+      </c>
+      <c r="D8">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>2.69</v>
+      </c>
+      <c r="B9">
+        <v>1.32</v>
+      </c>
+      <c r="C9">
+        <v>14.67</v>
+      </c>
+      <c r="D9">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>2.66</v>
+      </c>
+      <c r="B10">
+        <v>1.31</v>
+      </c>
+      <c r="C10">
+        <v>14.32</v>
+      </c>
+      <c r="D10">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>2.67</v>
+      </c>
+      <c r="B11">
+        <v>1.3</v>
+      </c>
+      <c r="C11">
+        <v>14.44</v>
+      </c>
+      <c r="D11">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
         <v>2.62</v>
       </c>
+      <c r="B12">
+        <v>1.29</v>
+      </c>
+      <c r="C12">
+        <v>13.68</v>
+      </c>
+      <c r="D12">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>2.67</v>
+      </c>
+      <c r="B13">
+        <v>1.3</v>
+      </c>
+      <c r="C13">
+        <v>14.49</v>
+      </c>
+      <c r="D13">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>2.67</v>
+      </c>
+      <c r="B14">
+        <v>1.32</v>
+      </c>
+      <c r="C14">
+        <v>14.5</v>
+      </c>
+      <c r="D14">
+        <v>3.73</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="22.25" customWidth="1"/>
+    <col min="2" max="2" width="21.375" customWidth="1"/>
+    <col min="3" max="3" width="18.375" customWidth="1"/>
+    <col min="4" max="4" width="31.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>2.66</v>
+      </c>
       <c r="B2">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="C2">
-        <v>13.68</v>
+        <v>14.24</v>
       </c>
       <c r="D2">
-        <v>3.5</v>
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>2.65</v>
+      </c>
+      <c r="B3">
+        <v>1.27</v>
+      </c>
+      <c r="C3">
+        <v>14.09</v>
+      </c>
+      <c r="D3">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>2.55</v>
+      </c>
+      <c r="B4">
+        <v>1.23</v>
+      </c>
+      <c r="C4">
+        <v>12.79</v>
+      </c>
+      <c r="D4">
+        <v>3.41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>2.58</v>
+      </c>
+      <c r="B5">
+        <v>1.2</v>
+      </c>
+      <c r="C5">
+        <v>13.23</v>
+      </c>
+      <c r="D5">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>2.56</v>
+      </c>
+      <c r="B6">
+        <v>1.19</v>
+      </c>
+      <c r="C6">
+        <v>12.92</v>
+      </c>
+      <c r="D6">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>2.52</v>
+      </c>
+      <c r="B7">
+        <v>1.21</v>
+      </c>
+      <c r="C7">
+        <v>12.43</v>
+      </c>
+      <c r="D7">
+        <v>3.36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>2.54</v>
+      </c>
+      <c r="B8">
+        <v>1.18</v>
+      </c>
+      <c r="C8">
+        <v>12.66</v>
+      </c>
+      <c r="D8">
+        <v>3.26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>2.51</v>
+      </c>
+      <c r="B9">
+        <v>1.19</v>
+      </c>
+      <c r="C9">
+        <v>12.33</v>
+      </c>
+      <c r="D9">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>2.49</v>
+      </c>
+      <c r="B10">
+        <v>1.19</v>
+      </c>
+      <c r="C10">
+        <v>12.1</v>
+      </c>
+      <c r="D10">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>2.5</v>
+      </c>
+      <c r="B11">
+        <v>1.19</v>
+      </c>
+      <c r="C11">
+        <v>12.14</v>
+      </c>
+      <c r="D11">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>2.43</v>
+      </c>
+      <c r="B12">
+        <v>1.17</v>
+      </c>
+      <c r="C12">
+        <v>11.41</v>
+      </c>
+      <c r="D12">
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>2.48</v>
+      </c>
+      <c r="B13">
+        <v>1.17</v>
+      </c>
+      <c r="C13">
+        <v>11.97</v>
+      </c>
+      <c r="D13">
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>2.49</v>
+      </c>
+      <c r="B14">
+        <v>1.16</v>
+      </c>
+      <c r="C14">
+        <v>12.08</v>
+      </c>
+      <c r="D14">
+        <v>3.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="23.625" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="20.875" customWidth="1"/>
+    <col min="4" max="4" width="26.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>2.62</v>
+      </c>
+      <c r="B2">
+        <v>1.24</v>
+      </c>
+      <c r="C2">
+        <v>13.72</v>
+      </c>
+      <c r="D2">
+        <v>3.44</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1459,7 +5132,7 @@
         <v>1.23</v>
       </c>
       <c r="C3">
-        <v>13.8</v>
+        <v>13.76</v>
       </c>
       <c r="D3">
         <v>3.43</v>
@@ -1470,27 +5143,27 @@
         <v>2.54</v>
       </c>
       <c r="B4">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="C4">
-        <v>12.69</v>
+        <v>12.65</v>
       </c>
       <c r="D4">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="B5">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="C5">
-        <v>13.31</v>
+        <v>13.25</v>
       </c>
       <c r="D5">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1498,13 +5171,13 @@
         <v>2.57</v>
       </c>
       <c r="B6">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="C6">
-        <v>13.11</v>
+        <v>13.09</v>
       </c>
       <c r="D6">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1515,35 +5188,35 @@
         <v>1.21</v>
       </c>
       <c r="C7">
-        <v>12.73</v>
+        <v>12.72</v>
       </c>
       <c r="D7">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="B8">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="C8">
-        <v>13.15</v>
+        <v>13.07</v>
       </c>
       <c r="D8">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="B9">
         <v>1.21</v>
       </c>
       <c r="C9">
-        <v>12.79</v>
+        <v>12.71</v>
       </c>
       <c r="D9">
         <v>3.36</v>
@@ -1557,10 +5230,10 @@
         <v>1.2</v>
       </c>
       <c r="C10">
-        <v>12.59</v>
+        <v>12.56</v>
       </c>
       <c r="D10">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1568,13 +5241,13 @@
         <v>2.54</v>
       </c>
       <c r="B11">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="C11">
-        <v>12.71</v>
+        <v>12.65</v>
       </c>
       <c r="D11">
-        <v>3.35</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1582,41 +5255,683 @@
         <v>2.48</v>
       </c>
       <c r="B12">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="C12">
-        <v>11.99</v>
+        <v>11.93</v>
       </c>
       <c r="D12">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="B13">
         <v>1.2</v>
       </c>
       <c r="C13">
-        <v>12.6</v>
+        <v>12.62</v>
       </c>
       <c r="D13">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="B14">
         <v>1.2</v>
       </c>
       <c r="C14">
-        <v>12.79</v>
+        <v>12.73</v>
       </c>
       <c r="D14">
         <v>3.33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="16.875" customWidth="1"/>
+    <col min="2" max="2" width="24.5" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="26.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>2.64</v>
+      </c>
+      <c r="B2">
+        <v>1.28</v>
+      </c>
+      <c r="C2">
+        <v>13.95</v>
+      </c>
+      <c r="D2">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>2.63</v>
+      </c>
+      <c r="B3">
+        <v>1.25</v>
+      </c>
+      <c r="C3">
+        <v>13.81</v>
+      </c>
+      <c r="D3">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>2.53</v>
+      </c>
+      <c r="B4">
+        <v>1.21</v>
+      </c>
+      <c r="C4">
+        <v>12.53</v>
+      </c>
+      <c r="D4">
+        <v>3.36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>2.57</v>
+      </c>
+      <c r="B5">
+        <v>1.19</v>
+      </c>
+      <c r="C5">
+        <v>13.03</v>
+      </c>
+      <c r="D5">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>2.54</v>
+      </c>
+      <c r="B6">
+        <v>1.19</v>
+      </c>
+      <c r="C6">
+        <v>12.74</v>
+      </c>
+      <c r="D6">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>2.51</v>
+      </c>
+      <c r="B7">
+        <v>1.19</v>
+      </c>
+      <c r="C7">
+        <v>12.27</v>
+      </c>
+      <c r="D7">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>2.53</v>
+      </c>
+      <c r="B8">
+        <v>1.18</v>
+      </c>
+      <c r="C8">
+        <v>12.52</v>
+      </c>
+      <c r="D8">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>2.5</v>
+      </c>
+      <c r="B9">
+        <v>1.18</v>
+      </c>
+      <c r="C9">
+        <v>12.16</v>
+      </c>
+      <c r="D9">
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>2.48</v>
+      </c>
+      <c r="B10">
+        <v>1.17</v>
+      </c>
+      <c r="C10">
+        <v>11.98</v>
+      </c>
+      <c r="D10">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>2.49</v>
+      </c>
+      <c r="B11">
+        <v>1.18</v>
+      </c>
+      <c r="C11">
+        <v>12.04</v>
+      </c>
+      <c r="D11">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>2.43</v>
+      </c>
+      <c r="B12">
+        <v>1.17</v>
+      </c>
+      <c r="C12">
+        <v>11.31</v>
+      </c>
+      <c r="D12">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>2.48</v>
+      </c>
+      <c r="B13">
+        <v>1.17</v>
+      </c>
+      <c r="C13">
+        <v>11.91</v>
+      </c>
+      <c r="D13">
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>2.48</v>
+      </c>
+      <c r="B14">
+        <v>1.16</v>
+      </c>
+      <c r="C14">
+        <v>11.98</v>
+      </c>
+      <c r="D14">
+        <v>3.19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="16.625" customWidth="1"/>
+    <col min="2" max="2" width="19.875" customWidth="1"/>
+    <col min="3" max="3" width="20.125" customWidth="1"/>
+    <col min="4" max="4" width="20.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>2.64</v>
+      </c>
+      <c r="B2">
+        <v>1.26</v>
+      </c>
+      <c r="C2">
+        <v>14.01</v>
+      </c>
+      <c r="D2">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>2.65</v>
+      </c>
+      <c r="B3">
+        <v>1.26</v>
+      </c>
+      <c r="C3">
+        <v>14.22</v>
+      </c>
+      <c r="D3">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>2.58</v>
+      </c>
+      <c r="B4">
+        <v>1.24</v>
+      </c>
+      <c r="C4">
+        <v>13.18</v>
+      </c>
+      <c r="D4">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>2.63</v>
+      </c>
+      <c r="B5">
+        <v>1.25</v>
+      </c>
+      <c r="C5">
+        <v>13.85</v>
+      </c>
+      <c r="D5">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>2.62</v>
+      </c>
+      <c r="B6">
+        <v>1.25</v>
+      </c>
+      <c r="C6">
+        <v>13.71</v>
+      </c>
+      <c r="D6">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>2.59</v>
+      </c>
+      <c r="B7">
+        <v>1.24</v>
+      </c>
+      <c r="C7">
+        <v>13.28</v>
+      </c>
+      <c r="D7">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>2.62</v>
+      </c>
+      <c r="B8">
+        <v>1.22</v>
+      </c>
+      <c r="C8">
+        <v>13.71</v>
+      </c>
+      <c r="D8">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>2.6</v>
+      </c>
+      <c r="B9">
+        <v>1.24</v>
+      </c>
+      <c r="C9">
+        <v>13.41</v>
+      </c>
+      <c r="D9">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>2.59</v>
+      </c>
+      <c r="B10">
+        <v>1.25</v>
+      </c>
+      <c r="C10">
+        <v>13.27</v>
+      </c>
+      <c r="D10">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>2.59</v>
+      </c>
+      <c r="B11">
+        <v>1.26</v>
+      </c>
+      <c r="C11">
+        <v>13.34</v>
+      </c>
+      <c r="D11">
+        <v>3.51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>2.53</v>
+      </c>
+      <c r="B12">
+        <v>1.23</v>
+      </c>
+      <c r="C12">
+        <v>12.53</v>
+      </c>
+      <c r="D12">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>2.59</v>
+      </c>
+      <c r="B13">
+        <v>1.22</v>
+      </c>
+      <c r="C13">
+        <v>13.28</v>
+      </c>
+      <c r="D13">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>2.59</v>
+      </c>
+      <c r="B14">
+        <v>1.22</v>
+      </c>
+      <c r="C14">
+        <v>13.36</v>
+      </c>
+      <c r="D14">
+        <v>3.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="18.25" customWidth="1"/>
+    <col min="2" max="2" width="19.625" customWidth="1"/>
+    <col min="3" max="3" width="26.375" customWidth="1"/>
+    <col min="4" max="4" width="39.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>2.62</v>
+      </c>
+      <c r="B2">
+        <v>1.26</v>
+      </c>
+      <c r="C2">
+        <v>13.79</v>
+      </c>
+      <c r="D2">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>2.62</v>
+      </c>
+      <c r="B3">
+        <v>1.24</v>
+      </c>
+      <c r="C3">
+        <v>13.68</v>
+      </c>
+      <c r="D3">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>2.52</v>
+      </c>
+      <c r="B4">
+        <v>1.21</v>
+      </c>
+      <c r="C4">
+        <v>12.41</v>
+      </c>
+      <c r="D4">
+        <v>3.36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>2.56</v>
+      </c>
+      <c r="B5">
+        <v>1.19</v>
+      </c>
+      <c r="C5">
+        <v>12.95</v>
+      </c>
+      <c r="D5">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>2.54</v>
+      </c>
+      <c r="B6">
+        <v>1.2</v>
+      </c>
+      <c r="C6">
+        <v>12.67</v>
+      </c>
+      <c r="D6">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>2.5</v>
+      </c>
+      <c r="B7">
+        <v>1.19</v>
+      </c>
+      <c r="C7">
+        <v>12.2</v>
+      </c>
+      <c r="D7">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>2.53</v>
+      </c>
+      <c r="B8">
+        <v>1.18</v>
+      </c>
+      <c r="C8">
+        <v>12.5</v>
+      </c>
+      <c r="D8">
+        <v>3.26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>2.5</v>
+      </c>
+      <c r="B9">
+        <v>1.17</v>
+      </c>
+      <c r="C9">
+        <v>12.13</v>
+      </c>
+      <c r="D9">
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>2.48</v>
+      </c>
+      <c r="B10">
+        <v>1.18</v>
+      </c>
+      <c r="C10">
+        <v>11.93</v>
+      </c>
+      <c r="D10">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>2.48</v>
+      </c>
+      <c r="B11">
+        <v>1.19</v>
+      </c>
+      <c r="C11">
+        <v>12</v>
+      </c>
+      <c r="D11">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>2.42</v>
+      </c>
+      <c r="B12">
+        <v>1.16</v>
+      </c>
+      <c r="C12">
+        <v>11.28</v>
+      </c>
+      <c r="D12">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>2.48</v>
+      </c>
+      <c r="B13">
+        <v>1.17</v>
+      </c>
+      <c r="C13">
+        <v>11.89</v>
+      </c>
+      <c r="D13">
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>2.48</v>
+      </c>
+      <c r="B14">
+        <v>1.16</v>
+      </c>
+      <c r="C14">
+        <v>11.99</v>
+      </c>
+      <c r="D14">
+        <v>3.19</v>
       </c>
     </row>
   </sheetData>
@@ -1631,10 +5946,10 @@
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="22.75" customWidth="1"/>
-    <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="18.25" customWidth="1"/>
-    <col min="4" max="4" width="22.375" customWidth="1"/>
+    <col min="1" max="1" width="17.5" customWidth="1"/>
+    <col min="2" max="2" width="16.3833333333333" customWidth="1"/>
+    <col min="3" max="3" width="17.6333333333333" customWidth="1"/>
+    <col min="4" max="4" width="21.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1653,16 +5968,16 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="B2">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="C2">
-        <v>13.66</v>
+        <v>13.68</v>
       </c>
       <c r="D2">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1670,13 +5985,13 @@
         <v>2.62</v>
       </c>
       <c r="B3">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="C3">
-        <v>13.74</v>
+        <v>13.8</v>
       </c>
       <c r="D3">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1684,13 +5999,13 @@
         <v>2.54</v>
       </c>
       <c r="B4">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="C4">
-        <v>12.63</v>
+        <v>12.69</v>
       </c>
       <c r="D4">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1701,7 +6016,7 @@
         <v>1.21</v>
       </c>
       <c r="C5">
-        <v>13.27</v>
+        <v>13.31</v>
       </c>
       <c r="D5">
         <v>3.36</v>
@@ -1712,27 +6027,27 @@
         <v>2.57</v>
       </c>
       <c r="B6">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="C6">
-        <v>13.12</v>
+        <v>13.11</v>
       </c>
       <c r="D6">
-        <v>3.43</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="B7">
         <v>1.21</v>
       </c>
       <c r="C7">
-        <v>12.76</v>
+        <v>12.73</v>
       </c>
       <c r="D7">
-        <v>3.34</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1740,13 +6055,13 @@
         <v>2.58</v>
       </c>
       <c r="B8">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="C8">
-        <v>13.14</v>
+        <v>13.15</v>
       </c>
       <c r="D8">
-        <v>3.32</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1754,27 +6069,27 @@
         <v>2.55</v>
       </c>
       <c r="B9">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="C9">
-        <v>12.82</v>
+        <v>12.79</v>
       </c>
       <c r="D9">
-        <v>3.33</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="B10">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="C10">
-        <v>12.64</v>
+        <v>12.59</v>
       </c>
       <c r="D10">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1782,13 +6097,13 @@
         <v>2.54</v>
       </c>
       <c r="B11">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="C11">
-        <v>12.63</v>
+        <v>12.71</v>
       </c>
       <c r="D11">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1796,27 +6111,27 @@
         <v>2.48</v>
       </c>
       <c r="B12">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="C12">
-        <v>11.98</v>
+        <v>11.99</v>
       </c>
       <c r="D12">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="B13">
         <v>1.2</v>
       </c>
       <c r="C13">
-        <v>12.66</v>
+        <v>12.6</v>
       </c>
       <c r="D13">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1824,13 +6139,13 @@
         <v>2.55</v>
       </c>
       <c r="B14">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="C14">
-        <v>12.77</v>
+        <v>12.79</v>
       </c>
       <c r="D14">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
     </row>
   </sheetData>
@@ -1845,10 +6160,10 @@
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="17.125" customWidth="1"/>
-    <col min="2" max="2" width="25.625" customWidth="1"/>
-    <col min="3" max="3" width="18.125" customWidth="1"/>
-    <col min="4" max="4" width="17.25" customWidth="1"/>
+    <col min="1" max="1" width="22.75" customWidth="1"/>
+    <col min="2" max="2" width="20.3833333333333" customWidth="1"/>
+    <col min="3" max="3" width="18.25" customWidth="1"/>
+    <col min="4" max="4" width="22.3833333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1867,170 +6182,170 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2">
-        <v>2.74</v>
+        <v>2.61</v>
       </c>
       <c r="B2">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="C2">
-        <v>15.56</v>
+        <v>13.66</v>
       </c>
       <c r="D2">
-        <v>3.96</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="B3">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="C3">
-        <v>15.23</v>
+        <v>13.74</v>
       </c>
       <c r="D3">
-        <v>3.77</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="B4">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="C4">
-        <v>13.87</v>
+        <v>12.63</v>
       </c>
       <c r="D4">
-        <v>3.7</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="B5">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="C5">
-        <v>14.34</v>
+        <v>13.27</v>
       </c>
       <c r="D5">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="B6">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="C6">
-        <v>13.97</v>
+        <v>13.12</v>
       </c>
       <c r="D6">
-        <v>3.53</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="B7">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="C7">
-        <v>13.45</v>
+        <v>12.76</v>
       </c>
       <c r="D7">
-        <v>3.53</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="B8">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="C8">
-        <v>13.67</v>
+        <v>13.14</v>
       </c>
       <c r="D8">
-        <v>3.46</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="B9">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="C9">
-        <v>13.37</v>
+        <v>12.82</v>
       </c>
       <c r="D9">
-        <v>3.46</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="B10">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="C10">
-        <v>13.03</v>
+        <v>12.64</v>
       </c>
       <c r="D10">
-        <v>3.45</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="B11">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="C11">
-        <v>12.99</v>
+        <v>12.63</v>
       </c>
       <c r="D11">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="B12">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="C12">
-        <v>12.25</v>
+        <v>11.98</v>
       </c>
       <c r="D12">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="B13">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="C13">
-        <v>12.79</v>
+        <v>12.66</v>
       </c>
       <c r="D13">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2041,7 +6356,7 @@
         <v>1.21</v>
       </c>
       <c r="C14">
-        <v>12.85</v>
+        <v>12.77</v>
       </c>
       <c r="D14">
         <v>3.34</v>
@@ -2059,10 +6374,10 @@
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="20.875" customWidth="1"/>
-    <col min="2" max="2" width="19.125" customWidth="1"/>
-    <col min="3" max="3" width="18.75" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="1" max="1" width="17.1333333333333" customWidth="1"/>
+    <col min="2" max="2" width="25.6333333333333" customWidth="1"/>
+    <col min="3" max="3" width="18.1333333333333" customWidth="1"/>
+    <col min="4" max="4" width="17.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2081,184 +6396,184 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="B2">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="C2">
-        <v>15.08</v>
+        <v>15.56</v>
       </c>
       <c r="D2">
-        <v>3.87</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="B3">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="C3">
-        <v>14.92</v>
+        <v>15.23</v>
       </c>
       <c r="D3">
-        <v>3.7</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="B4">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="C4">
-        <v>13.61</v>
+        <v>13.87</v>
       </c>
       <c r="D4">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="B5">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="C5">
-        <v>14.11</v>
+        <v>14.34</v>
       </c>
       <c r="D5">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="B6">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="C6">
-        <v>13.74</v>
+        <v>13.97</v>
       </c>
       <c r="D6">
-        <v>3.48</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="B7">
         <v>1.26</v>
       </c>
       <c r="C7">
-        <v>13.23</v>
+        <v>13.45</v>
       </c>
       <c r="D7">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="B8">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="C8">
-        <v>13.44</v>
+        <v>13.67</v>
       </c>
       <c r="D8">
-        <v>3.43</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="B9">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="C9">
-        <v>13.13</v>
+        <v>13.37</v>
       </c>
       <c r="D9">
-        <v>3.41</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="B10">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="C10">
-        <v>12.79</v>
+        <v>13.03</v>
       </c>
       <c r="D10">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="B11">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="C11">
-        <v>12.79</v>
+        <v>12.99</v>
       </c>
       <c r="D11">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="B12">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="C12">
-        <v>12.08</v>
+        <v>12.25</v>
       </c>
       <c r="D12">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="B13">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="C13">
-        <v>12.64</v>
+        <v>12.79</v>
       </c>
       <c r="D13">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="B14">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="C14">
-        <v>12.72</v>
+        <v>12.85</v>
       </c>
       <c r="D14">
-        <v>3.31</v>
+        <v>3.34</v>
       </c>
     </row>
   </sheetData>
@@ -2273,10 +6588,10 @@
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="21.375" customWidth="1"/>
-    <col min="3" max="3" width="24.75" customWidth="1"/>
-    <col min="4" max="4" width="37.5" customWidth="1"/>
+    <col min="1" max="1" width="20.8833333333333" customWidth="1"/>
+    <col min="2" max="2" width="19.1333333333333" customWidth="1"/>
+    <col min="3" max="3" width="18.75" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2295,184 +6610,184 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2">
-        <v>2.63</v>
+        <v>2.71</v>
       </c>
       <c r="B2">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="C2">
-        <v>13.82</v>
+        <v>15.08</v>
       </c>
       <c r="D2">
-        <v>3.52</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="B3">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="C3">
-        <v>13.67</v>
+        <v>14.92</v>
       </c>
       <c r="D3">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4">
-        <v>2.52</v>
+        <v>2.61</v>
       </c>
       <c r="B4">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="C4">
-        <v>12.47</v>
+        <v>13.61</v>
       </c>
       <c r="D4">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="B5">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="C5">
-        <v>12.98</v>
+        <v>14.11</v>
       </c>
       <c r="D5">
-        <v>3.32</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="B6">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="C6">
-        <v>12.75</v>
+        <v>13.74</v>
       </c>
       <c r="D6">
-        <v>3.37</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7">
-        <v>2.51</v>
+        <v>2.58</v>
       </c>
       <c r="B7">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="C7">
-        <v>12.28</v>
+        <v>13.23</v>
       </c>
       <c r="D7">
-        <v>3.28</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="B8">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="C8">
-        <v>12.63</v>
+        <v>13.44</v>
       </c>
       <c r="D8">
-        <v>3.25</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="B9">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="C9">
-        <v>12.2</v>
+        <v>13.13</v>
       </c>
       <c r="D9">
-        <v>3.29</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="B10">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="C10">
-        <v>12.12</v>
+        <v>12.79</v>
       </c>
       <c r="D10">
-        <v>3.24</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="B11">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="C11">
-        <v>12.1</v>
+        <v>12.79</v>
       </c>
       <c r="D11">
-        <v>3.28</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="B12">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="C12">
-        <v>11.42</v>
+        <v>12.08</v>
       </c>
       <c r="D12">
-        <v>3.24</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="B13">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="C13">
-        <v>12.04</v>
+        <v>12.64</v>
       </c>
       <c r="D13">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="B14">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="C14">
-        <v>12.15</v>
+        <v>12.72</v>
       </c>
       <c r="D14">
-        <v>3.21</v>
+        <v>3.31</v>
       </c>
     </row>
   </sheetData>
@@ -2487,10 +6802,10 @@
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="22.875" customWidth="1"/>
-    <col min="2" max="2" width="26.625" customWidth="1"/>
-    <col min="3" max="3" width="18.375" customWidth="1"/>
-    <col min="4" max="4" width="27.625" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="21.3833333333333" customWidth="1"/>
+    <col min="3" max="3" width="24.75" customWidth="1"/>
+    <col min="4" max="4" width="37.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2509,16 +6824,16 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="B2">
         <v>1.26</v>
       </c>
       <c r="C2">
-        <v>13.66</v>
+        <v>13.82</v>
       </c>
       <c r="D2">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2529,10 +6844,10 @@
         <v>1.24</v>
       </c>
       <c r="C3">
-        <v>13.58</v>
+        <v>13.67</v>
       </c>
       <c r="D3">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2543,7 +6858,7 @@
         <v>1.21</v>
       </c>
       <c r="C4">
-        <v>12.43</v>
+        <v>12.47</v>
       </c>
       <c r="D4">
         <v>3.36</v>
@@ -2557,10 +6872,10 @@
         <v>1.2</v>
       </c>
       <c r="C5">
-        <v>12.96</v>
+        <v>12.98</v>
       </c>
       <c r="D5">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2568,13 +6883,13 @@
         <v>2.55</v>
       </c>
       <c r="B6">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="C6">
         <v>12.75</v>
       </c>
       <c r="D6">
-        <v>3.31</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2582,6 +6897,220 @@
         <v>2.51</v>
       </c>
       <c r="B7">
+        <v>1.19</v>
+      </c>
+      <c r="C7">
+        <v>12.28</v>
+      </c>
+      <c r="D7">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>2.54</v>
+      </c>
+      <c r="B8">
+        <v>1.18</v>
+      </c>
+      <c r="C8">
+        <v>12.63</v>
+      </c>
+      <c r="D8">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>2.5</v>
+      </c>
+      <c r="B9">
+        <v>1.19</v>
+      </c>
+      <c r="C9">
+        <v>12.2</v>
+      </c>
+      <c r="D9">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>2.49</v>
+      </c>
+      <c r="B10">
+        <v>1.18</v>
+      </c>
+      <c r="C10">
+        <v>12.12</v>
+      </c>
+      <c r="D10">
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>2.49</v>
+      </c>
+      <c r="B11">
+        <v>1.19</v>
+      </c>
+      <c r="C11">
+        <v>12.1</v>
+      </c>
+      <c r="D11">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>2.44</v>
+      </c>
+      <c r="B12">
+        <v>1.18</v>
+      </c>
+      <c r="C12">
+        <v>11.42</v>
+      </c>
+      <c r="D12">
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>2.49</v>
+      </c>
+      <c r="B13">
+        <v>1.16</v>
+      </c>
+      <c r="C13">
+        <v>12.04</v>
+      </c>
+      <c r="D13">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>2.5</v>
+      </c>
+      <c r="B14">
+        <v>1.17</v>
+      </c>
+      <c r="C14">
+        <v>12.15</v>
+      </c>
+      <c r="D14">
+        <v>3.21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="22.8833333333333" customWidth="1"/>
+    <col min="2" max="2" width="26.6333333333333" customWidth="1"/>
+    <col min="3" max="3" width="18.3833333333333" customWidth="1"/>
+    <col min="4" max="4" width="27.6333333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>2.61</v>
+      </c>
+      <c r="B2">
+        <v>1.26</v>
+      </c>
+      <c r="C2">
+        <v>13.66</v>
+      </c>
+      <c r="D2">
+        <v>3.51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>2.61</v>
+      </c>
+      <c r="B3">
+        <v>1.24</v>
+      </c>
+      <c r="C3">
+        <v>13.58</v>
+      </c>
+      <c r="D3">
+        <v>3.44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>2.52</v>
+      </c>
+      <c r="B4">
+        <v>1.21</v>
+      </c>
+      <c r="C4">
+        <v>12.43</v>
+      </c>
+      <c r="D4">
+        <v>3.36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>2.56</v>
+      </c>
+      <c r="B5">
+        <v>1.2</v>
+      </c>
+      <c r="C5">
+        <v>12.96</v>
+      </c>
+      <c r="D5">
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>2.55</v>
+      </c>
+      <c r="B6">
+        <v>1.2</v>
+      </c>
+      <c r="C6">
+        <v>12.75</v>
+      </c>
+      <c r="D6">
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>2.51</v>
+      </c>
+      <c r="B7">
         <v>1.18</v>
       </c>
       <c r="C7">
@@ -2687,6 +7216,219 @@
       </c>
       <c r="D14">
         <v>3.21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="22.3333333333333" customWidth="1"/>
+    <col min="3" max="4" width="22.4416666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="3">
+        <v>2.94</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1.53</v>
+      </c>
+      <c r="C2" s="3">
+        <v>18.89</v>
+      </c>
+      <c r="D2" s="3">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="3">
+        <v>2.87</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1.44</v>
+      </c>
+      <c r="C3" s="3">
+        <v>17.68</v>
+      </c>
+      <c r="D3" s="3">
+        <v>4.24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="3">
+        <v>2.77</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="C4" s="3">
+        <v>15.91</v>
+      </c>
+      <c r="D4" s="3">
+        <v>4.07</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="3">
+        <v>2.78</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1.38</v>
+      </c>
+      <c r="C5" s="3">
+        <v>16.15</v>
+      </c>
+      <c r="D5" s="3">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="3">
+        <v>2.75</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1.34</v>
+      </c>
+      <c r="C6" s="3">
+        <v>15.57</v>
+      </c>
+      <c r="D6" s="3">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="3">
+        <v>2.71</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1.34</v>
+      </c>
+      <c r="C7" s="3">
+        <v>14.96</v>
+      </c>
+      <c r="D7" s="3">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="3">
+        <v>2.72</v>
+      </c>
+      <c r="B8" s="3">
+        <v>1.33</v>
+      </c>
+      <c r="C8" s="3">
+        <v>15.15</v>
+      </c>
+      <c r="D8" s="3">
+        <v>3.78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="3">
+        <v>2.7</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1.32</v>
+      </c>
+      <c r="C9" s="3">
+        <v>14.84</v>
+      </c>
+      <c r="D9" s="3">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="3">
+        <v>2.67</v>
+      </c>
+      <c r="B10" s="3">
+        <v>1.32</v>
+      </c>
+      <c r="C10" s="3">
+        <v>14.41</v>
+      </c>
+      <c r="D10" s="3">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="3">
+        <v>2.66</v>
+      </c>
+      <c r="B11" s="3">
+        <v>1.31</v>
+      </c>
+      <c r="C11" s="3">
+        <v>14.29</v>
+      </c>
+      <c r="D11" s="3">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="3">
+        <v>2.61</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="C12" s="3">
+        <v>13.54</v>
+      </c>
+      <c r="D12" s="3">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="3">
+        <v>2.65</v>
+      </c>
+      <c r="B13" s="3">
+        <v>1.29</v>
+      </c>
+      <c r="C13" s="3">
+        <v>14.2</v>
+      </c>
+      <c r="D13" s="3">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="3">
+        <v>2.65</v>
+      </c>
+      <c r="B14" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="C14" s="3">
+        <v>14.21</v>
+      </c>
+      <c r="D14" s="3">
+        <v>3.65</v>
       </c>
     </row>
   </sheetData>
